--- a/pcb_design/BOM_Ease_Appliances_PCBPower.xlsx
+++ b/pcb_design/BOM_Ease_Appliances_PCBPower.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Reference Designator</t>
+          <t>Designator</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
